--- a/results/models/ip_v1_SA_TOPSIS_Baseline_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
+++ b/results/models/ip_v1_SA_TOPSIS_Baseline_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
@@ -535,186 +535,186 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aydos Parkı</t>
+          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ADİL</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.96246645074015</v>
+        <v>40.98072340092061</v>
       </c>
       <c r="E4" t="n">
-        <v>29.25452742625226</v>
+        <v>29.26238410907338</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6165861487092867</v>
+        <v>0.2778922524034207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7021709272585134</v>
+        <v>0.8228922971943825</v>
       </c>
       <c r="I4" t="n">
-        <v>3.286399967276274</v>
+        <v>2.829412022600539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mehmet Akif Ersoy İlkokulu Bahçesi</t>
+          <t>Kanuni Sultan Süleyman Parkı</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>AHMET YESEVİ</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.95553928379504</v>
+        <v>40.97271700732063</v>
       </c>
       <c r="E5" t="n">
-        <v>29.25703415059688</v>
+        <v>29.27403441655196</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6958142516217007</v>
+        <v>0.2030739043182165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7928392367700497</v>
+        <v>0.8716925143245053</v>
       </c>
       <c r="I5" t="n">
-        <v>3.007514383478741</v>
+        <v>3.449481038576659</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adil Parkı</t>
+          <t>Mevlana Parkı</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>AKŞEMSETTİN</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.98660877990487</v>
+        <v>40.94874610580247</v>
       </c>
       <c r="E6" t="n">
-        <v>29.25958684878389</v>
+        <v>29.29872570873468</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>AKSEMSETTIN</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.05008946076687493</v>
+        <v>0.1772466657468486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8893784101140766</v>
+        <v>0.5825983080286559</v>
       </c>
       <c r="I6" t="n">
-        <v>2.290119772307221</v>
+        <v>4.393923909287198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Belediye Fen İşleri Önü Toplanma Alanı</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>BATTALGAZİ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40.97163567399593</v>
+        <v>40.98258840501005</v>
       </c>
       <c r="E7" t="n">
-        <v>29.26604512019534</v>
+        <v>29.26839981314643</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AHMET YESEVI</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.529419903877697</v>
+        <v>0.5188163076537894</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7711909396521685</v>
+        <v>0.91927042448959</v>
       </c>
       <c r="I7" t="n">
-        <v>3.651632287391553</v>
+        <v>3.23890601448014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mevlana Parkı</t>
+          <t>Muhsin Yazıcıoğlu Nikah Sarayı Önü Toplanma Alanı</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AKŞEMSETTİN</t>
+          <t>BATTALGAZİ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40.94874610580247</v>
+        <v>40.98310901587094</v>
       </c>
       <c r="E8" t="n">
-        <v>29.29872570873468</v>
+        <v>29.27005014068656</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AKSEMSETTIN</t>
+          <t>BATTALGAZI</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.1772466657468486</v>
+        <v>0.518151371522508</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5825983080286559</v>
+        <v>0.886711592943929</v>
       </c>
       <c r="I8" t="n">
-        <v>4.393923909287198</v>
+        <v>3.191227715326222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Belediye Fen İşleri Önü Toplanma Alanı</t>
+          <t>Şehit Hamit Sütmen Parkı</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.98258840501005</v>
+        <v>40.98181413193544</v>
       </c>
       <c r="E9" t="n">
-        <v>29.26839981314643</v>
+        <v>29.26881829375751</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5188163076537894</v>
+        <v>0.2465180065914853</v>
       </c>
       <c r="H9" t="n">
-        <v>0.91927042448959</v>
+        <v>0.9309992901953763</v>
       </c>
       <c r="I9" t="n">
-        <v>3.23890601448014</v>
+        <v>3.286130031389185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muhsin Yazıcıoğlu Nikah Sarayı Önü Toplanma Alanı</t>
+          <t>Şehit Öğretmen Hamit Sütmen İlkokulu ve Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40.98310901587094</v>
+        <v>40.98200942008475</v>
       </c>
       <c r="E10" t="n">
-        <v>29.27005014068656</v>
+        <v>29.26868471951212</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.518151371522508</v>
+        <v>0.3466916543834774</v>
       </c>
       <c r="H10" t="n">
-        <v>0.886711592943929</v>
+        <v>0.8953240933628536</v>
       </c>
       <c r="I10" t="n">
-        <v>3.191227715326222</v>
+        <v>3.274524837060275</v>
       </c>
     </row>
     <row r="11">
@@ -850,11 +850,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ahmet Yener Ortaokulu Bahçesi</t>
+          <t>Hüsnü M. Özyeğin Anadolu Lisesi Bahçesi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40.96521258412454</v>
+        <v>40.97099081886383</v>
       </c>
       <c r="E13" t="n">
-        <v>29.24991319728006</v>
+        <v>29.25230054133037</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.1888757829711</v>
+        <v>0.4788647468149812</v>
       </c>
       <c r="H13" t="n">
-        <v>0.707911693436899</v>
+        <v>0.8134050870318016</v>
       </c>
       <c r="I13" t="n">
-        <v>2.246565929038557</v>
+        <v>2.319717737621361</v>
       </c>
     </row>
     <row r="14">
@@ -1095,11 +1095,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Turgut Reis İlkokulu Bahçesi</t>
+          <t>Turgut Reis Parkı</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40.96614986801031</v>
+        <v>40.96256307543928</v>
       </c>
       <c r="E20" t="n">
-        <v>29.27966204899259</v>
+        <v>29.28139965617807</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.4433235964078843</v>
+        <v>0.02339639043034768</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7488221449191328</v>
+        <v>0.7690736177105905</v>
       </c>
       <c r="I20" t="n">
-        <v>3.099891657530684</v>
+        <v>3.929917873681156</v>
       </c>
     </row>
     <row r="21">
